--- a/data.mn/public/datasets/temperature-anomaly.xlsx
+++ b/data.mn/public/datasets/temperature-anomaly.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3012,6 +3012,16 @@
         <v>-3.6</v>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
